--- a/backtest_runs/20260410_193731/by_symbol/STYLERS/STYLERS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/STYLERS/STYLERS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-6542.69</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>93457.31</v>
@@ -771,7 +771,7 @@
         <v>-3729.109999999988</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>97677.68000000002</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>97677.68000000002</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>98325.25000000003</v>
@@ -1185,7 +1185,7 @@
         <v>-625.2400000000025</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>113621.3</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>113621.3</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>113621.3</v>
@@ -1323,7 +1323,7 @@
         <v>-1786.400000000009</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>111834.9</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>111834.9</v>
@@ -1461,7 +1461,7 @@
         <v>-6118.419999999988</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>105716.48</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>109892.19</v>
